--- a/TSMC_Phoenix_vs_Taiwan_Fab_Costs.xlsx
+++ b/TSMC_Phoenix_vs_Taiwan_Fab_Costs.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1471,7 +1471,7 @@
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>OVERALL WAFER PROCESSING COST</t>
+          <t>DICING, PACKAGING &amp; BACKEND COSTS (AZ-MADE CHIPS)</t>
         </is>
       </c>
       <c r="B38" s="5" t="n"/>
@@ -1483,75 +1483,773 @@
     <row r="39" ht="65" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Total Wafer Processing Cost (300mm, N4/N3)</t>
+          <t>Backend Process Flow (AZ chips)</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>~$17,000–$22,000/wafer</t>
+          <t>Wafers air-freighted to Taiwan for dicing, test &amp; packaging</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>~$15,500–$20,000/wafer</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>AZ ~10% higher overall</t>
+          <t>Dicing, test &amp; packaging done on-site or nearby OSAT (ASE/SPIL)</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>AZ adds logistics loop</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Per TechInsights Strategic Cost &amp; Price Model (Scotten Jones). Equipment dominance (~67%+ of cost) equalizes locations. Total difference is &lt;10%.</t>
+          <t>AZ wafers currently fly back to Taiwan via Eva Air for all backend processing (dicing, wafer probe, packaging, final test), then ship to end customers or assembly sites. This adds ~2–4 weeks transit time.</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>TechInsights Mar 2025 (Chip Insider, G. Dan Hutcheson); Silicon Analysts 2026; SemiWiki</t>
+          <t>SemiWiki (AZ chips flown to TW); TechPowerUp Feb 2025; inkl.com Mar 2025</t>
         </is>
       </c>
     </row>
     <row r="40" ht="65" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>Air Freight Cost (AZ→TW round trip)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Estimated ~$50–$150/wafer (specialized handling)</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>N/A (no shipping needed)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Added AZ cost</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>300mm wafers require specialized FOUPs, temperature/vibration control, and insurance. Air freight Taiwan↔USA is 1–5 days. Cost is modest per-wafer but adds up at volume; exact rates are negotiated privately.</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Wafer World (wafer shipping guide); FreightAmigo (TW→US routes); industry estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="65" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Wafer Dicing</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Done in Taiwan (same cost as TW-made wafers + freight)</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>~$30–$80/wafer (blade or laser dicing, 300mm)</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>AZ adds freight overhead</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Dicing cost itself is location-independent since performed in Taiwan for both. Laser dicing (&gt;42% market share) used for advanced nodes with thin wafers and 3D stacking. Global dicing services market: $614M (2024).</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Astute Analytica (dicing market); Han's Laser (300mm dicing methods); industry estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="65" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Wafer Probe / Wafer-Level Test</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Done in Taiwan (same cost as TW-made wafers)</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>~$100–$300/wafer (varies by test complexity)</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Same (done in TW)</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Wafer probe testing identifies good dies before packaging. Cost depends on number of test insertions, probe card costs (~$932/thousand probes), and test time. Test equipment ~8% of total fab equipment spend.</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>SemiconductorInsight (wafer test probe market); MDPI Electronics (multi-site test cost analysis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="65" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Packaging – Standard (FC-BGA)</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Done in Taiwan; ~$8/unit</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>~$8/unit</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Flip-chip BGA is the standard package for most logic chips. Price is set by OSAT providers (ASE, SPIL, Amkor) and is location-independent since both use Taiwan OSAT.</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Silicon Analysts 2026 (semiconductor cost guide); OSAT market data</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="65" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Packaging – InFO (Fan-Out WLP)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Done in Taiwan; ~$15/unit</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>~$15/unit</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>TSMC InFO used primarily for Apple A-series/M-series SoCs and MediaTek Dimensity. TSMC InFO revenue &gt;$3.5B/yr. Pricing identical since both sourced from TSMC Taiwan packaging.</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Silicon Analysts 2026; SemiconductorX (InFO overview); TechTicker (FOWLP market)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="65" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Packaging – CoWoS-S (2.5D)</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Done in Taiwan; ~$70/unit</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>~$70/unit</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>CoWoS-S is the dominant advanced package for AI/HPC chips (NVIDIA H100, AMD MI300). Demand exceeds supply by 40–50%, lead times 40–52 weeks. Prices rising ~20% over next 2 years.</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Silicon Analysts 2026; smbom.com (TSMC price hikes); Morgan Stanley estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="65" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Packaging – CoWoS-L (large interposer)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Done in Taiwan; ~$84–$98/unit (20–40% &gt; CoWoS-S)</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>~$84–$98/unit</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>CoWoS-L uses organic interposer for larger multi-die designs (NVIDIA B200 Blackwell). Higher cost due to interposer complexity and lower yields.</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Silicon Analysts packaging calculator; NVIDIA B200 cost breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="65" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Packaging – SoIC (3D Stacking)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Done in Taiwan; ~$120/unit</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>~$120/unit</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>TSMC SoIC enables 3D die stacking for highest-density integration. Currently lowest-volume, highest-cost option. Pricing is TSMC-set and location-independent.</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Silicon Analysts 2026; TSMC advanced packaging roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="65" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Full Backend Cost (H100-class AI chip)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>~$750–$1,100/chip (CoWoS-S/L + test + dicing) + AZ freight</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>~$750–$1,100/chip (CoWoS-S/L + test + dicing)</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>AZ adds ~$50–$150 freight</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>NVIDIA H100 SXM5 total COGS ~$3,320; CoWoS-S packaging alone ~$750. NVIDIA B200 total COGS ~$6,400 with CoWoS-L ~$1,100. Backend is 20–30% of total chip cost for AI accelerators.</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Silicon Analysts (H100/B200 cost breakdown); industry estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="65" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Backend as % of Total Chip Cost</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>~10–20% (standard); ~20–30% (AI/HPC with CoWoS)</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>~10–20% (standard); ~20–30% (AI/HPC with CoWoS)</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>Same % (same providers)</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Backend share is growing rapidly with advanced packaging complexity. OSAT providers raising prices 8–20%, memory packaging surcharges up 30%. Industry shift: backend becoming strategic differentiator.</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>SemiconductorX (backend overview); Silicon Analysts (chip price hikes 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="65" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>OSAT Price Trend</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>8–20% price hikes (2025–2026)</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>8–20% price hikes (2025–2026)</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>ASE expects advanced packaging/testing revenue to double in 2026. Near 90% utilization driving pricing power. Memory packaging surcharges up 30% due to AI server demand.</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Silicon Analysts (repricing wave); Digitimes Feb 2026 (ASE); SemiconductorX</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="25" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>GROSS MARGIN COMPARISON</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="65" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>TSMC Corporate Gross Margin (2025)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>59.9% full-year; 62.3% in Q4 2025</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>59.9% full-year; 62.3% in Q4 2025</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>N/A (consolidated)</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Company-wide margin. Up 3.8pp from 56.1% in 2024. Q4 2025 beat guidance (59–61%) by 1.3pp. Driven by N3 scaling, favorable FX, stronger pricing.</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Finovian (TSMC Q4 2025 earnings); MacroTrends (TSM gross margin); TSMC Q4 2025 results</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="65" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>TSMC Operating Margin (2025)</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>50.8% full-year; 54.0% in Q4 2025</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>50.8% full-year; 54.0% in Q4 2025</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>N/A (consolidated)</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Operating margin up 5.1pp from 45.7% in 2024. Net income ~$55.4B (NT$1,717B), +51.7% YoY.</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Finovian (TSMC Q4 2025 earnings); TSMC investor relations</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="65" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Arizona Fab Estimated Gross Margin</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>~8% (5nm production, est. 2025)</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>~50–60% (mature Taiwan fabs)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>AZ ~42–52pp lower</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>AZ 5nm production estimated at ~8% gross margin per White Hsu / Taiwan Tech Dispatch analysis. Low margin reflects: (1) new fab depreciation, (2) ramp-up phase, (3) all hidden efficiencies priced explicitly in US system. This is expected to improve over time.</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>White Hsu Blog (TSMC AZ low margins, Feb 2026); mbi-deepdives.com (TSMC's Margins)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="65" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Arizona Fab Net Profit (2025)</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>NT$161.4B (~$5.15B) profit</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>N/A (not separately reported)</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>First profitable year</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Dramatic turnaround from NT$142B loss in 2024 — a ~NT$300B swing. Driven by N4P ramp (began Q4 2024) + AI client demand. Government grants (25% of qualified investment) significantly aided financial performance.</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>BigGo Finance (TSMC AZ turnaround); TrendForce Mar 2026; AZ Tech Council; TSMC 2025 financial report</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="65" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Arizona Margin Dilution Impact</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>1–2% dilution to corporate margin (2025 est.)</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Manageable</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Overseas fabs (AZ+Japan+Germany) expected to dilute corporate gross margin by 2–3% in early stages, widening to 3–4% at scale. 2025 revised down to 1–2%. TSMC mitigates with premium pricing for 'geographic flexibility.'</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>mbi-deepdives.com (TSMC's Margins); BeyondSPX (margin dilution analysis); Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="65" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Wafer Price Premium (AZ vs TW)</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>5–20% premium charged to customers</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Baseline pricing</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>+5–20%</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>AMD CEO Lisa Su confirmed 5–20% premium for AZ-made chips. TSMC CEO C.C. Wei: charges for 'geographic flexibility' and considers 'made in USA' a premium product. Customers have agreed to pay premium.</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>The Verge (TSMC US chips premium); Yahoo Finance (TSMC AZ pricing); Taiwan News May 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="65" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Long-Term Margin Trajectory (AZ)</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Improving toward ~30–40% (analyst consensus 3–5 yr)</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Stable at ~50–60%</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Gap narrowing over time</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>AZ margins expected to improve as: (1) depreciation burden decreases, (2) yields improve (already 92% N4P vs 88% in Hsinchu), (3) local ecosystem matures, (4) Fab 2 &amp; 3 add scale. Unlikely to fully match Taiwan margins due to structural cost differences.</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Digitimes (AZ profitability milestone); ainvest.com (TSMC AZ catalyst); analyst consensus</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="65" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Key Margin Differentiator</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Cultural costs made explicit (formally priced labor, compliance, procedures)</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Cultural efficiencies absorbed informally (unpaid OT, flexible roles, implicit response)</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Per White Hsu analysis: Taiwan's high margins partly reflect 'invisible costs' — engineers returning to fabs without being called, blurred job roles, rapid cross-team action without formal escalation. In AZ, all these are formalized into explicit labor/compliance costs.</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>White Hsu Blog (TSMC AZ low margins, Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="25" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>OVERALL WAFER PROCESSING COST</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="65" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Total Wafer Processing Cost (300mm, N4/N3)</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>~$17,000–$22,000/wafer</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>~$15,500–$20,000/wafer</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>AZ ~10% higher overall</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Per TechInsights Strategic Cost &amp; Price Model (Scotten Jones). Equipment dominance (~67%+ of cost) equalizes locations. Total difference is &lt;10%.</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>TechInsights Mar 2025 (Chip Insider, G. Dan Hutcheson); Silicon Analysts 2026; SemiWiki</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="65" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Total Chip Cost incl. Backend (AI/HPC)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>~$3,500–$7,000/chip (wafer + backend + AZ freight)</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>~$3,300–$6,400/chip (wafer + backend)</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>AZ ~5–10% higher all-in</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>For AI accelerators (H100/B200 class). Frontend wafer cost is ~10% higher in AZ; backend costs identical (done in Taiwan); freight adds ~$50–150/wafer. All-in premium is lower than frontend-only premium.</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Silicon Analysts (H100/B200 COGS); TechInsights; calculated</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="65" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
           <t>Operating Cost Premium (all-in)</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Baseline + ~10%</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>+10%</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>Final TechInsights assessment. Earlier estimates of 30–50%+ premiums were based on construction costs and flawed labor assumptions. Equipment parity is decisive.</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>TechInsights Mar 2025; TechPowerUp Feb 2025 &amp; Mar 2025; TechSpot Mar 2025</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
@@ -1570,7 +2268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2443,6 +3141,446 @@
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>BigGo Finance – TSMC AZ $5.15B Profit Turnaround</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>https://finance.biggo.com/news/C_MZoZwBq7sy_YQMmt-O</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>TrendForce – TSMC 2025 Overseas Split</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>https://www.trendforce.com/news/2026/03/02/news-tsmcs-2025-overseas-split-china-leads-profits-arizona-turns-profitable-japan-losses-triple/</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>White Hsu Blog – TSMC AZ Fab Low Margins</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>https://whitehsu.blog/2026/02/09/tsmc-arizona-fab-low-margins/</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Finovian – TSMC Q4 2025 Earnings (62.3% GM)</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>https://finovian.com/category/earnings/tsmc-q4-2025-earnings-explained/</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>mbi-deepdives.com – TSMC's Margins</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mbi-deepdives.com/tsmcs-margins/</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>BeyondSPX – TSMC AI Supremacy &amp; Margin Dilution</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>https://beyondspx.com/quote/TSM/tsmc-s-ai-supremacy-meets-global-reality-why-margin-dilution-is-a-feature-not-a-bug-nyse-tsm</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>The Verge – TSMC US Chips Price Premium</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>https://on.theverge.com/news/712904/tsmcs-us-chips-come-at-a-premium</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan News – TSMC 30% Price Hike AZ Chips</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>https://www.taiwannews.com.tw/news/6114167</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Yahoo Finance – TSMC AZ Fab 21 Higher Price</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/tsmcs-arizona-fab-21-mass-114824172.html</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Silicon Analysts – Semiconductor Cost Guide 2026</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>https://siliconanalysts.com/guide/semiconductor-costs</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Silicon Analysts – Chip Price Hikes 2026</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>https://siliconanalysts.com/analysis/semiconductor-repricing-wave-price-hikes-reshape-chip-supply-chain</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Silicon Analysts – NVIDIA B200 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>https://siliconanalysts.com/analysis/nvidia-b200-blackwell-cost-breakdown</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Silicon Analysts – Adv. Packaging Cost Calculator</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>https://siliconanalysts.com/tools/packaging</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>SemiconductorX – Backend Assembly &amp; Test Overview</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>https://www.semiconductorx.com/back-end-assembly-overview.html</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>SemiWiki – TSMC AZ Chips Flown to Taiwan</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>https://semiwiki.com/forum/threads/tsmc-arizona-chips-are-reportedly-being-flown-back-to-taiwan-for-packaging-u-s-semiconductor-supply-chain-still-remains-dependent-on-taiwan.23109/</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Digitimes – TSMC AZ Profitability Milestone</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>https://www.digitimes.com/news/a20260302VL210/tsmc-arizona-fab-profit-2025.html</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Digitimes – ASE Advanced Packaging Revenue 2x</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>https://www.digitimes.com/news/a20260206PD224/packaging-ase-2026-testing-osat.html</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>AZ Tech Council – TSMC AZ First Profit</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>https://www.aztechcouncil.org/tsmcs-arizona-fab-generates-first-profit/</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Astute Analytica – Wafer Dicing Services Market</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>https://www.astuteanalytica.com/industry-report/wafer-dicing-services-market</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>MacroTrends – TSMC Gross Margin History</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>https://www.macrotrends.net/stocks/charts/TSM/taiwan-semiconductor-manufacturing/gross-margin</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>ainvest.com – TSMC AZ Bet Valuation Analysis</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ainvest.com/news/tsmc-arizona-bet-catalyst-valuation-costly-distraction-2601/</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Wafer World – Guide to Wafer Shipping</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>https://www.waferworld.com/post/guide-to-wafer-shipping</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -2463,7 +3601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2577,6 +3715,56 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>GROSS MARGIN: Arizona fab estimated at ~8% gross margin (5nm) vs ~50–60% for mature Taiwan fabs. The gap reflects new-fab depreciation, ramp-up costs, and explicit pricing of cultural efficiencies that are absorbed informally in Taiwan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>GROSS MARGIN: TSMC Arizona posted NT$161.4B ($5.15B) profit in 2025 — a dramatic turnaround from NT$142B loss in 2024. Government grants (25% of qualified investment) were critical. Corporate gross margin: 59.9% (2025), 62.3% in Q4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>GROSS MARGIN: TSMC charges a 5–20% wafer price premium for Arizona-made chips (per AMD CEO Lisa Su). CEO C.C. Wei frames it as charging for 'geographic flexibility' and 'made in USA' premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>BACKEND COSTS: All Arizona wafers currently ship back to Taiwan for dicing, testing, and packaging — adding ~$50–$150/wafer in air freight but using the same OSAT infrastructure as Taiwan-made wafers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>BACKEND COSTS: Advanced packaging (CoWoS-S at ~$70/unit, CoWoS-L at ~$84–98/unit, SoIC at ~$120/unit) is identical in cost for AZ and TW wafers since all packaging is done in Taiwan. Backend is 10–20% of standard chip cost, rising to 20–30% for AI/HPC with CoWoS.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>

--- a/TSMC_Phoenix_vs_Taiwan_Fab_Costs.xlsx
+++ b/TSMC_Phoenix_vs_Taiwan_Fab_Costs.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Cost Comparison" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Sources &amp; References" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Key Findings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AZ Expansion Phases" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +66,23 @@
       <color rgb="009C0006"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +105,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F7FB"/>
         <bgColor rgb="00F2F7FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCD5B4"/>
+        <bgColor rgb="00FCD5B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -167,6 +201,39 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2268,7 +2335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3583,6 +3650,426 @@
       <c r="D67" s="8" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>TrendForce – TSMC AZ Fab 2 3nm H2 2027</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>https://www.trendforce.com/news/2026/03/24/news-tsmc-reportedly-eyes-2h27-3nm-mass-production-at-arizona-fab-2-four-u-s-fabs-said-to-be-fully-booked/</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>theGPUTrade – TSMC Moves AZ Fab-2 to H2 2027</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>https://thegputrade.com/news/tsmc-moves-arizona-fab2-production-up-to-h2-2027-zz6u58ee</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>TechOvedas – TSMC Accelerates AZ to 2027</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>https://techovedas.com/tsmc-accelerates-arizona-fab-to-2027-2nm-a16-chips-and-the-future-of-u-s-semiconductor-strategy/</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Tom's Hardware – TSMC AZ Fab 21 4nm Production</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>https://aztechcouncil.org/tsmc-arizona-fab21-already-making-4nm-chips</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Jan 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Tom's Hardware – TSMC Speeds Up 2nm AZ Plans</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/tech-industry/tsmc-moves-up-2nm-production-plans-in-arizona-ceo-also-hints-at-further-site-expansion-beyond-usd165-billion-commitment</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Jul 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>TechPowerUp – TSMC CoPoS/SoIC for AZ Fab</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>https://www.techpowerup.com/338847/tsmc-plans-copos-and-soic-advanced-packaging-for-arizona-fab</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Jul 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>FinancialContent – TSMC AZ 92% Yield</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>https://markets.financialcontent.com/wedbush/article/tokenring-2025-12-24-silicon-sovereignty-tsmc-arizona-hits-92-yield-as-3nm-equipment-arrives-for-2027-powerhouse</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Barchart – TSMC Fab 4 Fully Booked</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>https://www.barchart.com/story/news/927456/taiwan-semiconductor-s-new-fab-4-is-fully-booked-before-construction-even-begins</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Benzinga – TSMC Supply Squeeze Through 2028</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>https://www.benzinga.com/markets/tech/26/03/51558739/tsmc-supply-squeeze-2028-chipmaker-opportunity-ai-demand-nvidia-apple</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Silicon Analysts – Foundry Allocation Q1 2026</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>https://siliconanalysts.com/analysis/foundry-allocation-status-q1-2026</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>AZ Central – Apple 100M TSMC AZ Chips 2026</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>https://azcentral.com/story/money/business/tech/2026/02/27/apple-to-buy-100-million-tsmc-arizona-chips-in-2026/88888519007/</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>AZ Central – TSMC Hiring Thousands for $165B</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>https://www.azcentral.com/story/money/business/tech/2025/03/13/tsmc-will-need-to-fill-thousands-of-jobs/81760910007/</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Axios Phoenix – TSMC Workforce Growth</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/phoenix/2025/05/06/tsmc-arizona-hiring-workforce-growth</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>PCMag – TSMC 3 New Fabs $100B Investment</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>https://uk.pcmag.com/processors/156935/tsmc-to-build-3-new-us-fabs-with-100-billion-investment</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>InBusinessPHX – TSMC Additional Fabs/AP/R&amp;D</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>https://inbusinessphx.com/semi-insights/tsmc-to-build-additional-three-fabs-two-advanced-packaging-facilities-and-rd-center-in-arizona</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>CNBC – TSMC AZ Expansion Not Done (CFO)</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/01/16/tsmcs-arizona-chip-expansion-isnt-done-after-us-investment-cfo.html</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Wedbush – TSMC AZ Gigafab Cluster $165B</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>https://investor.wedbush.com/wedbush/article/tokenring-2026-1-23-tsmcs-arizona-gigafab-cluster-scales-up-with-165-billion-total-investment</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Yahoo Finance – TSMC $100B Additional AZ Investment</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/tsmc-considers-additional-100-billion-153658229.html</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>TrendForce – TSMC 2nm US, 1nm Tainan</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>https://www.trendforce.com/news/2025/02/03/news-tsmc-said-to-plan-2nm-production-in-u-s-1nm-fab-in-tainan/</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Feb 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>IndustrialInfo – TSMC 2026 CapEx $52-56B</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>https://www.industrialinfo.com/news/article/chipmaker-tsmc-projects-2026-capex-will-reach-52-billion-56-billion--352061</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>FinancialContent – TSMC AZ CoWoS Plant</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>https://www.financialcontent.com/article/tokenring-2026-1-15-arizona-silicon-fortress-tsmc-accelerates-3nm-expansion-and-plans-us-based-cowos-plant</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
         </is>
       </c>
     </row>
@@ -3771,4 +4258,825 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TSMC Arizona Fab Expansion: Phase-by-Phase Status (as of Mar 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="35" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Total committed investment: $165B (potentially $265B incl. additional $100B announced Mar 2025). Complex: 6 fabs + 2 advanced packaging facilities + 1 R&amp;D center on ~2,000 acres in North Phoenix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Process Node</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Announced</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Production Start</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Capacity (WPM)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Key Details</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>FABRICATION PLANTS (6 FABS)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Fab 21 Phase 1</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>N4P / N5 (4nm-class)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>OPERATIONAL</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>May 2020</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Q4 2024 (HVM early 2025)</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>10K→30K WPM (ramping)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>First operational US advanced fab. 92% yield on N4P (exceeds Taiwan's 88%). Producing: Apple A16 Bionic, Apple S9, AMD Ryzen 9000, NVIDIA Blackwell GPUs (Oct 2025). Apple committed 100M+ chips in 2026. First profitable year: 2025 (NT$161.4B / $5.15B profit). Chips currently fly to Taiwan for backend, but Amkor Peoria AZ handles some Apple packaging.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Wikipedia (TSMC AZ); Tom's Hardware Jan 2025; AZ Central Feb 2026; TrendForce Feb 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Fab 21 Phase 2</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>N3 (3nm-class)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION COMPLETE
+Tool install 2026</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Dec 2022</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>H2 2027 (accelerated from 2028)</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>~20K WPM (est.)</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Building construction completed 2025. Equipment move-in planned 2026; tool installation Q3 2026. Timeline accelerated by ~6 months — compressed from 6 quarters to 4–5 quarters. TSMC sending more personnel to AZ to speed cleanroom prep and MEP engineering. Capacity already booked by major customers.</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>TrendForce Mar 2026; Digitimes Dec 2025; theGPUTrade; Wikipedia (TSMC AZ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Fab 21 Phase 3</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N2 / A16 (2nm / 1.6nm)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>UNDER CONSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Apr 2024</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2029 (originally; some reports say 2027 accelerated)</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Broke ground April 2025. Will use nanosheet transistor architecture (GAA). A16 (1.6nm) includes backside power delivery — TSMC's most advanced process. Conflicting timelines: Wikipedia says 2029; TechOvedas reported acceleration to 2027. Part of the original $65B commitment (3 fabs).</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Wikipedia (TSMC AZ); TechOvedas; Tom's Hardware Jul 2025; NIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Fab 21 Phase 4</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>TBD (likely N2/A16+)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>~2030 (est.)</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Part of the additional $100B commitment (3 more fabs) announced Mar 2025 at White House with TSMC CEO C.C. Wei. Fully booked by customers before construction begins (Apple, NVIDIA, AMD, Broadcom, Qualcomm). Permits filed; scheduling is demand-driven.</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Barchart (Fab 4 fully booked); PCMag Mar 2025; Wikipedia (TSMC AZ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Fab 21 Phase 5</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Part of the 6-fab gigafab cluster. Limited public details. CEO C.C. Wei: at completion, AZ gigafab will represent 30% of TSMC's 2nm-and-beyond capacity. CFO indicated expansion isn't done even after $165B commitment.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>CNBC Jan 2026; AZ Central Jul 2025; Wikipedia (TSMC AZ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Fab 21 Phase 6</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Final fab in the 6-fab gigafab cluster. Very early planning stages. Process node and timeline to be determined by market demand and technology roadmap. TSMC acquired ~900 additional acres adjacent to original 1,100-acre site for total ~2,000-acre complex.</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Wikipedia (TSMC AZ); Wedbush Investor Jan 2026; BlackRidge Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SUPPORTING FACILITIES</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Adv. Packaging 1 (AP1)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>CoWoS / CoPoS / SoIC</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Late 2029 / Early 2030</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>First US-based advanced packaging. Groundbreaking slated 2028. CoPoS pilot line as early as 2026; partner validation late 2027. Partnership with Amkor Technology (Peoria, AZ) for final assembly. Critical for eliminating the current need to fly wafers back to Taiwan for packaging.</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>TechPowerUp (CoPoS/SoIC plans); FinancialContent Jan 2026; Amkor press release Oct 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Adv. Packaging 2 (AP2)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Second advanced packaging facility. Very early planning. Part of the gigafab cluster announcement. Will help TSMC localize more of the backend supply chain in the US.</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Wikipedia (TSMC AZ); InBusinessPHX; NIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>R&amp;D Center</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Research and development center as part of the gigafab cluster. Will support process development and yield optimization for US-based manufacturing. Part of broader strategy to build self-sufficient semiconductor ecosystem in Arizona.</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Wikipedia (TSMC AZ); PCMag Mar 2025; NIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>KEY METRICS &amp; MILESTONES</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Total Investment</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>$165B pledged (potentially $265B with additional $100B)</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t>PCMag Mar 2025; Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Federal Subsidies</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>$6.6B direct CHIPS Act grants + $5B loans</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>Reuters Nov 2024; NIST</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>Total Site Area</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>~2,000 acres (original 1,100 + 900 additional acres acquired)</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="26" t="inlineStr">
+        <is>
+          <t>Wedbush Investor Jan 2026; Wikipedia</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>Direct Manufacturing Jobs</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>~6,000 (at full buildout)</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>NIST; AZ Central Mar 2025</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Current Employees (2024)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>~3,000 (growing to ~6,000 within a few years)</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>AZ Central Mar 2025; Axios Phoenix May 2025</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Construction Jobs</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>~20,000+ over project lifetime</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="28" t="inlineStr">
+        <is>
+          <t>NIST; AZ Commerce Authority</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Key Customers (Booked)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Apple (100M+ chips 2026), NVIDIA (largest TSMC customer), AMD, Qualcomm, Broadcom</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>AZ Central Feb 2026; Barchart; Silicon Analysts Q1 2026</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>AZ Share of Advanced Capacity</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>30% of 2nm-and-beyond capacity at full buildout</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="28" t="inlineStr">
+        <is>
+          <t>AZ Central Jul 2025; Wikipedia</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Yield Achievement</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>92% N4P yield (exceeds Taiwan's 88% for same node)</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="26" t="inlineStr">
+        <is>
+          <t>FinancialContent Dec 2025; SemiWiki</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Build Time Compression</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Reduced from ~3 years (Fab 1) to ~1.5–2 years (subsequent fabs)</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="27" t="n"/>
+      <c r="G27" s="28" t="inlineStr">
+        <is>
+          <t>TrendForce Mar 2026</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>2026 CapEx (Company-wide)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>$52–56B (+40% vs 2025); significant Arizona allocation</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="26" t="inlineStr">
+        <is>
+          <t>IndustrialInfo; Tom's Hardware May 2025</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Halo Vista Development</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>3,500-acre mixed-use development adjacent to TSMC site (Sonoran Oasis Research &amp; Tech Park)</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>AZ Central Oct 2024; AZ Central Mar 2026</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Key Supplier Partnerships</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Amkor (packaging, Peoria AZ); Linde (N₂, O₂, Ar); Air Liquide (H₂, He, CO₂)</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="26" t="inlineStr">
+        <is>
+          <t>Amkor Oct 2024; Linde Sep 2021; Air Liquide Jan 2022</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B26:F26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/TSMC_Phoenix_vs_Taiwan_Fab_Costs.xlsx
+++ b/TSMC_Phoenix_vs_Taiwan_Fab_Costs.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Sources &amp; References" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Key Findings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="AZ Expansion Phases" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Yields &amp; Capacity" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,8 +82,14 @@
       <color rgb="00555555"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -125,6 +132,12 @@
         <bgColor rgb="00FCD5B4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -152,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -234,6 +247,26 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2335,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4070,6 +4103,346 @@
       <c r="D88" s="6" t="inlineStr">
         <is>
           <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>TechSoda – TSMC AZ 100% Capacity Utilization</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>https://techsoda.substack.com/p/tsmc-arizonas-first-fab-to-reach</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>diskmfr.com – TSMC Global Fab Capacity Overview</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>https://www.diskmfr.com/tsmc-global-fab-capacity-and-process-node-overview/</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>globalsemiresearch – TSMC Fab Capacity by Wafer Size 2025</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>https://globalsemiresearch.substack.com/p/tsmcs-fab-wafer-capacity-breakdown</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>TSMC Official – Fab Capacity Page</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tsmc.com/english/dedicatedFoundry/manufacturing/fab_capacity</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>TechPowerUp – TSMC 2nm Surpasses 90% Yield</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>https://www.techpowerup.com/337668/tsmc-reportedly-surpasses-90-production-yield-rate-with-2-nm-process</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Digitimes – TSMC 2nm Yield by Product Type</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>https://www.digitimes.com/news/a20250325PD228/tsmc-2nm-fab-yield-rate-2025.html</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Digitimes – TSMC 3nm/5nm Utilization &gt;100% Q1 2025</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>https://www.digitimes.com/news/a20250226PD245/tsmc-5nm-3nm-chips-2025.html</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Feb 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>WCCFTech – TSMC 3nm 160K WPM Golden Period</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>https://wccftech.com/tsmc-3nm-golden-period-of-mass-production-has-started-says-report/</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>AnandTech – TSMC N5 Better Yield Than N7</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>https://www.anandtech.com/print/16028/better-yield-on-5nm-than-7nm-tsmc-update-on-defect-rates-for-n5</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>guru3d – TSMC 3nm Yields 60–80%</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>https://www.guru3d.com/story/tsmc-3nm-yields-between-60-and-80/</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Comkex – TSMC N3P On Track</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>https://comkex.com/tech/tsmc-performance-optimized-3nm-n3p-process-on-track-for-mass-production-this-year/</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>topcpu.net – TSMC 2nm 90% Yield Trial</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.topcpu.net/pl/news/tsmc-completes-trial-production-of-2nm-process-with-an-impressive-90-percent-yield</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>heqingele.com – TSMC 2nm Yield Surge 2026</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>https://heqingele.com/blog/tsmc-2nm-yield-rates-mass-production-status-2026/</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>StreetsTocker – TSMC 2nm 50K to 140K Wafers</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>https://streetstocker.com/tsmc-2nm-capacity-constraints-2026/</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>SMM – TSMC N3 100 NTOs</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>https://news.metal.com/newscontent/103631957/TSMCs-Luo-Zhenqiu:-N3-Has-Secured-Approximately-100-NTOs-and-Is-Expected-to-Become-a-High-Production-Long-Running-Process-Period</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>smbom.com – TSMC 3nm/5nm 100% Utilization</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>https://www.smbom.com/news/45772</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>FinancialContent – TSMC AZ Blackwell HVM</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>https://markets.financialcontent.com/bpas/article/tokenring-2026-2-5-silicon-sovereignty-nvidia-and-tsmc-achieve-high-volume-blackwell-production-on-us-soil</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
         </is>
       </c>
     </row>
@@ -5079,4 +5452,857 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TSMC Yields &amp; Wafer Capacity: Arizona vs Taiwan Fabs (as of Q1 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="35" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>TSMC does not officially disclose yield rates. Figures are from analyst reports, media, and industry estimates. Total TSMC capacity: ~1.3M wafers/month (~17M+ wafers/year, 12-inch equivalent). Advanced nodes (≤7nm) = 77% of Q4 2025 wafer revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Fab / Location</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Process Node</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Yield Rate (est.)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Capacity (WPM)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Utilization</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>ARIZONA (Phoenix, USA)</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Fab 21 Phase 1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>N4P / N4 (4nm)</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>~92%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>15K → 24K WPM
+(ramping; target 30K)</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>~100%
+(approaching)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>92% yield exceeds Taiwan Hsinchu's 88% for same N4P node. Producing Apple A16, S9, AMD Ryzen 9000, NVIDIA Blackwell (from Oct 2025). Apple committed 100M+ chips in 2026. 'Copy-exactly' strategy from Taiwan achieved yield parity.</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>FinancialContent Dec 2025 (92% yield); TechSoda (100% util); Wikipedia (TSMC AZ); Tom's HW Jan 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Fab 21 Phase 1</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>N5 (5nm family)</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>~88–92%</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>(shared with N4P above)</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>~100%</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA Blackwell B200 uses custom 4NP variant (5nm family). Silicon yields in high-80% to low-90% range. 5nm is a mature node for TSMC; AZ yields match Taiwan levels.</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>FinancialContent Feb 2026 (Blackwell production); SemiWiki (AZ near 100% capacity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fab 21 Phase 2</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>N3 (3nm)</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>N/A (not yet in production)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>~20K WPM (est. target)</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Building complete. Tool install Q3 2026. HVM targeted H2 2027. Expected to benefit from Phase 1 learning — yields likely to ramp faster than Taiwan's initial N3 ramp.</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>TrendForce Mar 2026; theGPUTrade; Digitimes Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Fab 21 Phase 3</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>N2 / A16 (2nm / 1.6nm)</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>N/A (under construction)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Under construction (broke ground Apr 2025). Production targeted 2029. GAA nanosheet architecture. Backside power delivery for A16.</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Wikipedia (TSMC AZ); TechOvedas; Tom's HW Jul 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TAIWAN (Hsinchu, Tainan, Taichung)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Fab 18 P1–P3
+(Tainan)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>N4 / N4P (4nm)</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>~88%</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>~60K WPM
+(part of 120K P1–P6)</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>~100%</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Primary 4nm production base. Hot-run premiums 50–100% with lead times 39–52 weeks (Q1 2026). AZ Fab 21 Phase 1 actually exceeds this yield (~92% vs ~88%). Mature node, fully booked.</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>diskmfr.com (fab overview); Silicon Analysts Q1 2026 (allocation); FinancialContent Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Fab 18 P4–P6
+(Tainan)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>N3 / N3E / N3P (3nm)</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>~75–85% (maturing)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>~60K WPM
+(part of 120K P1–P6;
+ramping to 160K total N3)</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>&gt;100%</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>3nm mass production since 2024. N3E defect density at parity with N5 for same lifecycle point. N3P yields 'close to N3E.' 3nm = 28% of Q4 2025 wafer revenue. Severely constrained: lead times 52–78 weeks.</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Silicon Analysts Q1 2026; WCCFTech (160K WPM target); guru3d (60–80% early); Digitimes Q1 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Fab 18 P7–P8
+(Tainan)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>N3 (3nm expansion)</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>~80–85% (est.)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Expansion underway
+(→ 160K total N3 by late 2025)</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Ramping</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Expanding Fab 18 3nm capacity. Combined P4–P8 targeting 160K WPM for N3 by end of 2025. ~100 NTOs secured by Sep 2025. N3 expected to be 'high-production, long-running' node.</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>WCCFTech (N3 golden period); SMM (100 NTOs); diskmfr.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Fab 12
+(Hsinchu)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>N7 / N7+ (7nm)</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>~90%+ (mature)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>~132–135K WPM
+(all nodes in Fab 12)</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Mature 7nm production. Also produces 10nm, 12nm, 16nm, 20nm. Capacity declining slightly (135K Q1 → 132K Q4 2025) as advanced demand shifts to Fab 18. 7nm = 14% of Q4 2025 wafer revenue.</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>globalsemiresearch (fab capacity); diskmfr.com; TSMC Q4 2025 results</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Fab 12
+(Hsinchu)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>N5 / N4 (5nm/4nm)</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>~90%+ (mature)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>(included in 132–135K above)</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>&gt;100%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>5nm is fully mature with yields better than 7nm (per TSMC). 5nm = 35% of Q4 2025 wafer revenue. 100% utilization in Q1 2025. Driven by NVIDIA Blackwell, Apple, AMD demand.</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>AnandTech (N5 yields &gt; N7); Digitimes Q1 2025 (100% util); TSMC Q4 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Fab 15
+(Taichung)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>N16 / N20 (16nm/20nm)</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>~95%+ (very mature)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>~166K WPM</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Moderate–High</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Mature 16/20nm production base. Began production 2012. Serves HPC, networking, consumer applications. Stable yields on well-established processes.</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>diskmfr.com (fab overview); Wikipedia (TSMC fabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Fab 14
+(Tainan)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>N28+ (28nm and above)</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>~95%+ (very mature)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Specialty process production: RF, high voltage, embedded memory/flash. Serves automotive, IoT, industrial. 28nm HV for automotive power management, 40nm RF-SOI for 5G, 55nm embedded flash.</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>diskmfr.com (fab overview)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Fab 20
+(Hsinchu Baoshan)</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>N2 (2nm)</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>~70–90% (trial→HVM)</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>3K–3.5K WPM (2025)
+→ 120K WPM (end 2026)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Ramping</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>2nm R&amp;D and mass production base. Trial production achieved 90% yield (memory products, Q1 2025). Logic yields 70–80% as of Jan 2026. GAA nanosheet technology. HVM entered Jan 2026. Combined with Kaohsiung Fab 22: targeting 50K WPM by end 2025, 120–140K by end 2026.</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>TechPowerUp (90% trial yield); topcpu.net; heqingele.com; FinancialContent Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>OTHER OVERSEAS FABS (for context)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Fab 16
+(Nanjing, China)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>N16/N12 + N28</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>~90%+ (mature)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>~24K WPM (16/12nm)
++ 50K WPM (28nm P2)</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Most profitable overseas fab (NT$274.5B profit 2025) due to reduced depreciation. Phase 1: 16/12nm. Phase 2: 28nm (accepted Oct 2024, +600K wafers/yr).</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>diskmfr.com; BigGo Finance (TSMC 2025 overseas); TrendForce Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>JASM Fab 1
+(Kumamoto, Japan)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>N22/N28 + N12/N16</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Ramping</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>~55K WPM (target)</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Low (ramping)</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Mass production from end of 2024. Posted NT$97.7B loss in 2025 — adjustment phase, capacity not yet utilized. Serves automotive and mature-process demand.</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>diskmfr.com; TrendForce Mar 2026; BigGo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>YIELD &amp; CAPACITY COMPARISON SUMMARY</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="34" t="n"/>
+      <c r="D23" s="34" t="n"/>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="34" t="n"/>
+      <c r="G23" s="34" t="n"/>
+    </row>
+    <row r="24" ht="55" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>N4P Yield: AZ vs TW</t>
+        </is>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>AZ: ~92% | TW (Fab 18): ~88%</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>Arizona EXCEEDS Taiwan by ~4 percentage points on the same N4P node — a notable achievement for the first US advanced fab.</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>FinancialContent Dec 2025; multiple corroborating sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="55" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>N3 Yield (TW only so far)</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>TW: ~75–85% (maturing)</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>N3E defect density at parity with N5. N3P yields close to N3E. 3nm is entering 'golden period.' AZ Phase 2 N3 not yet in production (H2 2027).</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="28" t="inlineStr">
+        <is>
+          <t>guru3d; TSMC Comkex (N3P); WCCFTech</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="55" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>N2 Yield (TW only so far)</t>
+        </is>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>TW: 90% (trial) → 70–80% (HVM)</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>Impressive trial yield on memory; logic HVM yields 70–80% as of Jan 2026. AZ Phase 3 N2 not until 2029.</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="26" t="inlineStr">
+        <is>
+          <t>TechPowerUp; topcpu.net; heqingele.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="55" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>AZ Capacity vs TW Total</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="inlineStr">
+        <is>
+          <t>AZ: ~15–24K WPM | TW: ~1.27M WPM</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>Arizona is currently ~1.2–1.9% of total TSMC 12-inch capacity. At full 6-fab buildout, AZ will represent 30% of 2nm+ capacity.</t>
+        </is>
+      </c>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="27" t="n"/>
+      <c r="G27" s="28" t="inlineStr">
+        <is>
+          <t>TechSoda; globalsemiresearch; TSMC official</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="55" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Capacity by Revenue Node (Q4 2025)</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>N3: 28% | N5: 35% | N7: 14%</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>Advanced nodes (≤7nm) = 77% of wafer revenue. N3+N5 together = 63% of revenue. N3 capacity severely constrained (52–78 week lead times).</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="26" t="inlineStr">
+        <is>
+          <t>TSMC Q4 2025 results; Silicon Analysts Q1 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="55" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Utilization Rate</t>
+        </is>
+      </c>
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>N3/N5: &gt;100% | AZ N4P: ~100%</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>Both Taiwan and Arizona advanced fabs are at or above full utilization. TSMC overall 2024 utilization &gt;95%. 4 US fabs already fully booked.</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>Digitimes Q1 2025; TechSoda; TrendForce Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="55" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Key Takeaway</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="inlineStr"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>Arizona has ACHIEVED yield parity (and in N4P, surpassed Taiwan) on its operational node. The 'copy-exactly' strategy works. Capacity remains a fraction of Taiwan, but is scaling. Backend packaging remains Taiwan-dependent until AP1 comes online (~2030).</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="26" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A23:G23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>